--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132892100</v>
+        <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>87508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Adolfsbergsskogen öster om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652502</v>
+        <v>652442</v>
       </c>
       <c r="R2" t="n">
-        <v>6650117</v>
+        <v>6650210</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,8 +770,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>F-8583</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,68 +793,65 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892100</t>
+          <t>https://artportalen.se/Sighting/136753526</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132889679</v>
+        <v>136753515</v>
       </c>
       <c r="B3" t="n">
-        <v>57269</v>
+        <v>87549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Adolfsbergsskogen öster om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652469</v>
+        <v>652442</v>
       </c>
       <c r="R3" t="n">
-        <v>6650249</v>
+        <v>6650210</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,8 +889,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>F-8580 F-8581</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -906,73 +912,65 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889679</t>
+          <t>https://artportalen.se/Sighting/136753515</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132892109</v>
+        <v>136753372</v>
       </c>
       <c r="B4" t="n">
-        <v>57269</v>
+        <v>93440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Adolfsbergsskogen öster om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652502</v>
+        <v>652406</v>
       </c>
       <c r="R4" t="n">
-        <v>6650117</v>
+        <v>6650289</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +1008,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,16 +1026,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892109</t>
+          <t>https://artportalen.se/Sighting/136753372</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132889677</v>
+        <v>136753380</v>
       </c>
       <c r="B5" t="n">
-        <v>57568</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,51 +1043,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102963</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Adolfsbergsskogen öster om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652469</v>
+        <v>652407</v>
       </c>
       <c r="R5" t="n">
-        <v>6650249</v>
+        <v>6650285</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,12 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,16 +1140,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889677</t>
+          <t>https://artportalen.se/Sighting/136753380</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132892500</v>
+        <v>132892100</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,16 +1157,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102963</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R6" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,38 +1256,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892500</t>
+          <t>https://artportalen.se/Sighting/132892100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132892806</v>
+        <v>132889679</v>
       </c>
       <c r="B7" t="n">
-        <v>57568</v>
+        <v>57269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1314,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652547</v>
+        <v>652469</v>
       </c>
       <c r="R7" t="n">
-        <v>6650113</v>
+        <v>6650249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,38 +1372,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892806</t>
+          <t>https://artportalen.se/Sighting/132889679</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132893072</v>
+        <v>132892109</v>
       </c>
       <c r="B8" t="n">
-        <v>57568</v>
+        <v>57269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,9 +1411,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1430,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652486</v>
+        <v>652502</v>
       </c>
       <c r="R8" t="n">
-        <v>6650197</v>
+        <v>6650117</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,16 +1493,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893072</t>
+          <t>https://artportalen.se/Sighting/132892109</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132889698</v>
+        <v>132889677</v>
       </c>
       <c r="B9" t="n">
-        <v>58519</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,16 +1510,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>102963</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1530,14 +1532,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1612,16 +1609,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889698</t>
+          <t>https://artportalen.se/Sighting/132889677</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132892114</v>
+        <v>132892500</v>
       </c>
       <c r="B10" t="n">
-        <v>58519</v>
+        <v>57568</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,16 +1626,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>102963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,14 +1648,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1672,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652502</v>
+        <v>652363</v>
       </c>
       <c r="R10" t="n">
-        <v>6650117</v>
+        <v>6650308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,16 +1725,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892114</t>
+          <t>https://artportalen.se/Sighting/132892500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132892517</v>
+        <v>132892806</v>
       </c>
       <c r="B11" t="n">
-        <v>58519</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,16 +1742,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>102963</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1772,14 +1764,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1793,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652363</v>
+        <v>652547</v>
       </c>
       <c r="R11" t="n">
-        <v>6650308</v>
+        <v>6650113</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1854,16 +1841,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892517</t>
+          <t>https://artportalen.se/Sighting/132892806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889680</v>
+        <v>132893072</v>
       </c>
       <c r="B12" t="n">
-        <v>58410</v>
+        <v>57568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,21 +1858,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>102963</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1909,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652469</v>
+        <v>652486</v>
       </c>
       <c r="R12" t="n">
-        <v>6650249</v>
+        <v>6650197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,16 +1957,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889680</t>
+          <t>https://artportalen.se/Sighting/132893072</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132892093</v>
+        <v>132889698</v>
       </c>
       <c r="B13" t="n">
-        <v>58410</v>
+        <v>58519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,21 +1974,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2009,9 +1996,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2025,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R13" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,16 +2078,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892093</t>
+          <t>https://artportalen.se/Sighting/132889698</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132892506</v>
+        <v>132892114</v>
       </c>
       <c r="B14" t="n">
-        <v>58410</v>
+        <v>58519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2125,9 +2117,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2141,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R14" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,33 +2199,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892506</t>
+          <t>https://artportalen.se/Sighting/132892114</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132410216</v>
+        <v>132892517</v>
       </c>
       <c r="B15" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2241,7 +2238,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>hane</t>
@@ -2252,17 +2248,21 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652436</v>
+        <v>652363</v>
       </c>
       <c r="R15" t="n">
-        <v>6650254</v>
+        <v>6650308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,22 +2289,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,38 +2320,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132410216</t>
+          <t>https://artportalen.se/Sighting/132892517</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132889696</v>
+        <v>132889680</v>
       </c>
       <c r="B16" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2369,14 +2359,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2451,38 +2436,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889696</t>
+          <t>https://artportalen.se/Sighting/132889680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132892112</v>
+        <v>132892093</v>
       </c>
       <c r="B17" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2490,14 +2475,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2572,38 +2552,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892112</t>
+          <t>https://artportalen.se/Sighting/132892093</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132892518</v>
+        <v>132892506</v>
       </c>
       <c r="B18" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2611,14 +2591,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2693,13 +2668,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892518</t>
+          <t>https://artportalen.se/Sighting/132892506</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132892813</v>
+        <v>132410216</v>
       </c>
       <c r="B19" t="n">
         <v>58349</v>
@@ -2732,6 +2707,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>hane</t>
@@ -2742,21 +2718,17 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652547</v>
+        <v>652436</v>
       </c>
       <c r="R19" t="n">
-        <v>6650113</v>
+        <v>6650254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2783,12 +2755,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,13 +2796,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892813</t>
+          <t>https://artportalen.se/Sighting/132410216</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133159721</v>
+        <v>132889696</v>
       </c>
       <c r="B20" t="n">
         <v>58349</v>
@@ -2853,24 +2835,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652397</v>
+        <v>652469</v>
       </c>
       <c r="R20" t="n">
-        <v>6650215</v>
+        <v>6650249</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2894,22 +2886,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2924,44 +2906,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159721</t>
+          <t>https://artportalen.se/Sighting/132889696</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132892516</v>
+        <v>132892112</v>
       </c>
       <c r="B21" t="n">
-        <v>58134</v>
+        <v>58349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2995,10 +2977,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R21" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3056,33 +3038,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892516</t>
+          <t>https://artportalen.se/Sighting/132892112</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132893086</v>
+        <v>132892518</v>
       </c>
       <c r="B22" t="n">
-        <v>58134</v>
+        <v>58349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3116,10 +3098,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R22" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,38 +3159,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893086</t>
+          <t>https://artportalen.se/Sighting/132892518</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133159949</v>
+        <v>132892813</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3216,24 +3198,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>652397</v>
+        <v>652547</v>
       </c>
       <c r="R23" t="n">
-        <v>6650215</v>
+        <v>6650113</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3257,22 +3249,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,27 +3269,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159949</t>
+          <t>https://artportalen.se/Sighting/132892813</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132889687</v>
+        <v>133159721</v>
       </c>
       <c r="B24" t="n">
-        <v>58131</v>
+        <v>58349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3315,16 +3297,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103023</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3337,34 +3319,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>652469</v>
+        <v>652397</v>
       </c>
       <c r="R24" t="n">
-        <v>6650249</v>
+        <v>6650215</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3388,12 +3360,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,44 +3390,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889687</t>
+          <t>https://artportalen.se/Sighting/133159721</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132892104</v>
+        <v>132892516</v>
       </c>
       <c r="B25" t="n">
-        <v>58131</v>
+        <v>58134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3479,10 +3461,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>652502</v>
+        <v>652363</v>
       </c>
       <c r="R25" t="n">
-        <v>6650117</v>
+        <v>6650308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3540,33 +3522,33 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892104</t>
+          <t>https://artportalen.se/Sighting/132892516</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133159854</v>
+        <v>132893086</v>
       </c>
       <c r="B26" t="n">
-        <v>58131</v>
+        <v>58134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3579,24 +3561,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652397</v>
+        <v>652486</v>
       </c>
       <c r="R26" t="n">
-        <v>6650215</v>
+        <v>6650197</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3620,22 +3612,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3650,49 +3632,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159854</t>
+          <t>https://artportalen.se/Sighting/132893086</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132889685</v>
+        <v>133159949</v>
       </c>
       <c r="B27" t="n">
-        <v>58596</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103041</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3705,24 +3687,19 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652469</v>
+        <v>652397</v>
       </c>
       <c r="R27" t="n">
-        <v>6650249</v>
+        <v>6650215</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3746,12 +3723,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3766,27 +3753,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889685</t>
+          <t>https://artportalen.se/Sighting/133159949</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132892102</v>
+        <v>132889687</v>
       </c>
       <c r="B28" t="n">
-        <v>58596</v>
+        <v>58131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3794,21 +3781,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3837,10 +3824,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R28" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3898,16 +3885,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892102</t>
+          <t>https://artportalen.se/Sighting/132889687</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132892513</v>
+        <v>132892104</v>
       </c>
       <c r="B29" t="n">
-        <v>58596</v>
+        <v>58131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3915,21 +3902,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3958,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R29" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4019,33 +4006,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892513</t>
+          <t>https://artportalen.se/Sighting/132892104</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132850969</v>
+        <v>133159854</v>
       </c>
       <c r="B30" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4069,13 +4056,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>652496</v>
+        <v>652397</v>
       </c>
       <c r="R30" t="n">
-        <v>6650123</v>
+        <v>6650215</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4099,22 +4086,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4140,38 +4127,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132850969</t>
+          <t>https://artportalen.se/Sighting/133159854</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132892118</v>
+        <v>132889685</v>
       </c>
       <c r="B31" t="n">
-        <v>58624</v>
+        <v>58596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4179,14 +4166,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4200,10 +4182,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R31" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4261,16 +4243,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892118</t>
+          <t>https://artportalen.se/Sighting/132889685</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132666098</v>
+        <v>132892102</v>
       </c>
       <c r="B32" t="n">
-        <v>58658</v>
+        <v>58596</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4278,21 +4260,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4300,24 +4282,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>652496</v>
+        <v>652502</v>
       </c>
       <c r="R32" t="n">
-        <v>6650123</v>
+        <v>6650117</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4341,22 +4333,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4371,27 +4353,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132666098</t>
+          <t>https://artportalen.se/Sighting/132892102</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132850906</v>
+        <v>132892513</v>
       </c>
       <c r="B33" t="n">
-        <v>58658</v>
+        <v>58596</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4399,21 +4381,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4421,24 +4403,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>652397</v>
+        <v>652363</v>
       </c>
       <c r="R33" t="n">
-        <v>6650215</v>
+        <v>6650308</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4462,22 +4454,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4492,44 +4474,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132850906</t>
+          <t>https://artportalen.se/Sighting/132892513</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132889683</v>
+        <v>132850969</v>
       </c>
       <c r="B34" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4544,27 +4526,22 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>652469</v>
+        <v>652496</v>
       </c>
       <c r="R34" t="n">
-        <v>6650249</v>
+        <v>6650123</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4588,12 +4565,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4608,44 +4595,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889683</t>
+          <t>https://artportalen.se/Sighting/132850969</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132892117</v>
+        <v>132892118</v>
       </c>
       <c r="B35" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4740,13 +4727,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892117</t>
+          <t>https://artportalen.se/Sighting/132892118</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132892522</v>
+        <v>132666098</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4779,34 +4766,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>652363</v>
+        <v>652496</v>
       </c>
       <c r="R36" t="n">
-        <v>6650308</v>
+        <v>6650123</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4830,12 +4807,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4850,24 +4837,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892522</t>
+          <t>https://artportalen.se/Sighting/132666098</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132892816</v>
+        <v>132850906</v>
       </c>
       <c r="B37" t="n">
         <v>58658</v>
@@ -4900,34 +4887,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>652547</v>
+        <v>652397</v>
       </c>
       <c r="R37" t="n">
-        <v>6650113</v>
+        <v>6650215</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4951,12 +4928,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4971,24 +4958,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892816</t>
+          <t>https://artportalen.se/Sighting/132850906</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132893090</v>
+        <v>132889683</v>
       </c>
       <c r="B38" t="n">
         <v>58658</v>
@@ -5021,14 +5008,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5042,10 +5024,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>652486</v>
+        <v>652469</v>
       </c>
       <c r="R38" t="n">
-        <v>6650197</v>
+        <v>6650249</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5103,38 +5085,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893090</t>
+          <t>https://artportalen.se/Sighting/132889683</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132892115</v>
+        <v>132892117</v>
       </c>
       <c r="B39" t="n">
-        <v>58698</v>
+        <v>58658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5224,38 +5206,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892115</t>
+          <t>https://artportalen.se/Sighting/132892117</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132892510</v>
+        <v>132892522</v>
       </c>
       <c r="B40" t="n">
-        <v>58698</v>
+        <v>58658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5345,38 +5327,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892510</t>
+          <t>https://artportalen.se/Sighting/132892522</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132893083</v>
+        <v>132892816</v>
       </c>
       <c r="B41" t="n">
-        <v>58698</v>
+        <v>58658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5405,10 +5387,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>652486</v>
+        <v>652547</v>
       </c>
       <c r="R41" t="n">
-        <v>6650197</v>
+        <v>6650113</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5466,68 +5448,73 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893083</t>
+          <t>https://artportalen.se/Sighting/132892816</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133159810</v>
+        <v>132893090</v>
       </c>
       <c r="B42" t="n">
-        <v>58698</v>
+        <v>58658</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>652397</v>
+        <v>652486</v>
       </c>
       <c r="R42" t="n">
-        <v>6650215</v>
+        <v>6650197</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5551,22 +5538,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5581,44 +5558,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159810</t>
+          <t>https://artportalen.se/Sighting/132893090</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132892807</v>
+        <v>132892115</v>
       </c>
       <c r="B43" t="n">
-        <v>58107</v>
+        <v>58698</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5631,9 +5608,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5647,10 +5629,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>652547</v>
+        <v>652502</v>
       </c>
       <c r="R43" t="n">
-        <v>6650113</v>
+        <v>6650117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5708,33 +5690,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892807</t>
+          <t>https://artportalen.se/Sighting/132892115</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132893075</v>
+        <v>132892510</v>
       </c>
       <c r="B44" t="n">
-        <v>58107</v>
+        <v>58698</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5747,9 +5729,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5763,10 +5750,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R44" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5824,38 +5811,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893075</t>
+          <t>https://artportalen.se/Sighting/132892510</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134462233</v>
+        <v>132893083</v>
       </c>
       <c r="B45" t="n">
-        <v>56854</v>
+        <v>58698</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205995</v>
+        <v>103055</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5863,25 +5850,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storvreta NO, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>652363</v>
+        <v>652486</v>
       </c>
       <c r="R45" t="n">
-        <v>6650308</v>
+        <v>6650197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5908,27 +5901,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Förbiflygande några gånger</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5954,16 +5932,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134462233</t>
+          <t>https://artportalen.se/Sighting/132893083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132659867</v>
+        <v>133159810</v>
       </c>
       <c r="B46" t="n">
-        <v>56833</v>
+        <v>58698</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,50 +5949,51 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Wängelistorpet, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>652369</v>
+        <v>652397</v>
       </c>
       <c r="R46" t="n">
-        <v>6650236</v>
+        <v>6650215</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6038,12 +6017,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6058,67 +6047,76 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132659867</t>
+          <t>https://artportalen.se/Sighting/133159810</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134462221</v>
+        <v>132892807</v>
       </c>
       <c r="B47" t="n">
-        <v>56833</v>
+        <v>58107</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205998</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storvreta NO, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>652363</v>
+        <v>652547</v>
       </c>
       <c r="R47" t="n">
-        <v>6650308</v>
+        <v>6650113</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6145,27 +6143,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Förbiflygande många gånger</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6191,65 +6174,68 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134462221</t>
+          <t>https://artportalen.se/Sighting/132892807</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>57751934</v>
+        <v>132893075</v>
       </c>
       <c r="B48" t="n">
-        <v>92328</v>
+        <v>58107</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040162</v>
+        <v>205976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>652461</v>
+        <v>652486</v>
       </c>
       <c r="R48" t="n">
-        <v>6650195</v>
+        <v>6650197</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6273,17 +6259,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tallstubbe</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6292,29 +6273,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6329,6 +6289,512 @@
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132893075</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134462233</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56854</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storvreta NO, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Förbiflygande några gånger</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134462233</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132659867</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Wängelistorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>652369</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6650236</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132659867</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134462221</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storvreta NO, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Förbiflygande många gånger</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134462221</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>57751934</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>652461</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6650195</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/57751934</t>
         </is>
@@ -6383,6 +6849,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87508</v>
+        <v>87510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,59 +799,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136753515</v>
+        <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87549</v>
+        <v>87510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3739</v>
+        <v>462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Violettrandad spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius pseudoglaucopus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Jul.Schäff. ex M.M.Moser) Quadr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen öster om, Upl</t>
+          <t>Adolfbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652442</v>
+        <v>652435</v>
       </c>
       <c r="R3" t="n">
-        <v>6650210</v>
+        <v>6650211</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +867,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Känd förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,35 +900,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>F-8580 F-8581</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Åke Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Åke Berg, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136753515</t>
+          <t>https://artportalen.se/Sighting/136772120</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136753372</v>
+        <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>93440</v>
+        <v>87551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -964,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652406</v>
+        <v>652442</v>
       </c>
       <c r="R4" t="n">
-        <v>6650289</v>
+        <v>6650210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,6 +1014,11 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>F-8580 F-8581</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1026,16 +1033,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136753372</t>
+          <t>https://artportalen.se/Sighting/136753515</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136753380</v>
+        <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652407</v>
+        <v>652406</v>
       </c>
       <c r="R5" t="n">
-        <v>6650285</v>
+        <v>6650289</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1140,16 +1147,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136753380</t>
+          <t>https://artportalen.se/Sighting/136753372</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132892100</v>
+        <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,51 +1164,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Adolfsbergsskogen öster om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652502</v>
+        <v>652407</v>
       </c>
       <c r="R6" t="n">
-        <v>6650117</v>
+        <v>6650285</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1243,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,38 +1261,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892100</t>
+          <t>https://artportalen.se/Sighting/136753380</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132889679</v>
+        <v>132892100</v>
       </c>
       <c r="B7" t="n">
-        <v>57269</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652469</v>
+        <v>652502</v>
       </c>
       <c r="R7" t="n">
-        <v>6650249</v>
+        <v>6650117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,13 +1377,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889679</t>
+          <t>https://artportalen.se/Sighting/132892100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132892109</v>
+        <v>132889679</v>
       </c>
       <c r="B8" t="n">
         <v>57269</v>
@@ -1411,14 +1416,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R8" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,38 +1493,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892109</t>
+          <t>https://artportalen.se/Sighting/132889679</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132889677</v>
+        <v>132892109</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>57269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1532,9 +1532,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652469</v>
+        <v>652502</v>
       </c>
       <c r="R9" t="n">
-        <v>6650249</v>
+        <v>6650117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,13 +1614,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889677</t>
+          <t>https://artportalen.se/Sighting/132892109</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132892500</v>
+        <v>132889677</v>
       </c>
       <c r="B10" t="n">
         <v>57568</v>
@@ -1650,7 +1655,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652363</v>
+        <v>652469</v>
       </c>
       <c r="R10" t="n">
-        <v>6650308</v>
+        <v>6650249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,13 +1730,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892500</t>
+          <t>https://artportalen.se/Sighting/132889677</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132892806</v>
+        <v>132892500</v>
       </c>
       <c r="B11" t="n">
         <v>57568</v>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652547</v>
+        <v>652363</v>
       </c>
       <c r="R11" t="n">
-        <v>6650113</v>
+        <v>6650308</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,13 +1846,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892806</t>
+          <t>https://artportalen.se/Sighting/132892500</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132893072</v>
+        <v>132892806</v>
       </c>
       <c r="B12" t="n">
         <v>57568</v>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652486</v>
+        <v>652547</v>
       </c>
       <c r="R12" t="n">
-        <v>6650197</v>
+        <v>6650113</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,16 +1962,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893072</t>
+          <t>https://artportalen.se/Sighting/132892806</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132889698</v>
+        <v>132893072</v>
       </c>
       <c r="B13" t="n">
-        <v>58519</v>
+        <v>57568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,16 +1979,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>102963</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1996,14 +2001,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652469</v>
+        <v>652486</v>
       </c>
       <c r="R13" t="n">
-        <v>6650249</v>
+        <v>6650197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2078,13 +2078,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889698</t>
+          <t>https://artportalen.se/Sighting/132893072</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132892114</v>
+        <v>132889698</v>
       </c>
       <c r="B14" t="n">
         <v>58519</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R14" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,13 +2199,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892114</t>
+          <t>https://artportalen.se/Sighting/132889698</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132892517</v>
+        <v>132892114</v>
       </c>
       <c r="B15" t="n">
         <v>58519</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R15" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,16 +2320,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892517</t>
+          <t>https://artportalen.se/Sighting/132892114</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132889680</v>
+        <v>132892517</v>
       </c>
       <c r="B16" t="n">
-        <v>58410</v>
+        <v>58519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2359,9 +2359,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2375,10 +2380,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652469</v>
+        <v>652363</v>
       </c>
       <c r="R16" t="n">
-        <v>6650249</v>
+        <v>6650308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2436,13 +2441,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889680</t>
+          <t>https://artportalen.se/Sighting/132892517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132892093</v>
+        <v>132889680</v>
       </c>
       <c r="B17" t="n">
         <v>58410</v>
@@ -2491,10 +2496,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R17" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2552,13 +2557,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892093</t>
+          <t>https://artportalen.se/Sighting/132889680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132892506</v>
+        <v>132892093</v>
       </c>
       <c r="B18" t="n">
         <v>58410</v>
@@ -2607,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R18" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,38 +2673,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892506</t>
+          <t>https://artportalen.se/Sighting/132892093</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132410216</v>
+        <v>132892506</v>
       </c>
       <c r="B19" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2707,28 +2712,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652436</v>
+        <v>652363</v>
       </c>
       <c r="R19" t="n">
-        <v>6650254</v>
+        <v>6650308</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,22 +2758,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,13 +2789,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132410216</t>
+          <t>https://artportalen.se/Sighting/132892506</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132889696</v>
+        <v>132410216</v>
       </c>
       <c r="B20" t="n">
         <v>58349</v>
@@ -2835,6 +2828,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>hane</t>
@@ -2845,21 +2839,17 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652469</v>
+        <v>652436</v>
       </c>
       <c r="R20" t="n">
-        <v>6650249</v>
+        <v>6650254</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,12 +2876,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,13 +2917,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889696</t>
+          <t>https://artportalen.se/Sighting/132410216</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132892112</v>
+        <v>132889696</v>
       </c>
       <c r="B21" t="n">
         <v>58349</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R21" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,13 +3038,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892112</t>
+          <t>https://artportalen.se/Sighting/132889696</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132892518</v>
+        <v>132892112</v>
       </c>
       <c r="B22" t="n">
         <v>58349</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R22" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,13 +3159,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892518</t>
+          <t>https://artportalen.se/Sighting/132892112</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132892813</v>
+        <v>132892518</v>
       </c>
       <c r="B23" t="n">
         <v>58349</v>
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>652547</v>
+        <v>652363</v>
       </c>
       <c r="R23" t="n">
-        <v>6650113</v>
+        <v>6650308</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,13 +3280,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892813</t>
+          <t>https://artportalen.se/Sighting/132892518</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133159721</v>
+        <v>132892813</v>
       </c>
       <c r="B24" t="n">
         <v>58349</v>
@@ -3319,24 +3319,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>652397</v>
+        <v>652547</v>
       </c>
       <c r="R24" t="n">
-        <v>6650215</v>
+        <v>6650113</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3360,22 +3370,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,44 +3390,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159721</t>
+          <t>https://artportalen.se/Sighting/132892813</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132892516</v>
+        <v>133159721</v>
       </c>
       <c r="B25" t="n">
-        <v>58134</v>
+        <v>58349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3440,34 +3440,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>652363</v>
+        <v>652397</v>
       </c>
       <c r="R25" t="n">
-        <v>6650308</v>
+        <v>6650215</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3491,12 +3481,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3511,24 +3511,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892516</t>
+          <t>https://artportalen.se/Sighting/133159721</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132893086</v>
+        <v>132892516</v>
       </c>
       <c r="B26" t="n">
         <v>58134</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R26" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3643,16 +3643,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893086</t>
+          <t>https://artportalen.se/Sighting/132892516</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133159949</v>
+        <v>132893086</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>58134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3682,24 +3682,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652397</v>
+        <v>652486</v>
       </c>
       <c r="R27" t="n">
-        <v>6650215</v>
+        <v>6650197</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3723,22 +3733,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3753,49 +3753,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159949</t>
+          <t>https://artportalen.se/Sighting/132893086</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132889687</v>
+        <v>133159949</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3803,34 +3803,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652469</v>
+        <v>652397</v>
       </c>
       <c r="R28" t="n">
-        <v>6650249</v>
+        <v>6650215</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3854,12 +3844,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,24 +3874,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889687</t>
+          <t>https://artportalen.se/Sighting/133159949</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132892104</v>
+        <v>132889687</v>
       </c>
       <c r="B29" t="n">
         <v>58131</v>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R29" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4006,13 +4006,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892104</t>
+          <t>https://artportalen.se/Sighting/132889687</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133159854</v>
+        <v>132892104</v>
       </c>
       <c r="B30" t="n">
         <v>58131</v>
@@ -4045,24 +4045,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>652397</v>
+        <v>652502</v>
       </c>
       <c r="R30" t="n">
-        <v>6650215</v>
+        <v>6650117</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4086,22 +4096,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4116,27 +4116,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159854</t>
+          <t>https://artportalen.se/Sighting/132892104</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132889685</v>
+        <v>133159854</v>
       </c>
       <c r="B31" t="n">
-        <v>58596</v>
+        <v>58131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103041</v>
+        <v>103023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4168,27 +4168,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>652469</v>
+        <v>652397</v>
       </c>
       <c r="R31" t="n">
-        <v>6650249</v>
+        <v>6650215</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4212,12 +4207,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4232,24 +4237,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889685</t>
+          <t>https://artportalen.se/Sighting/133159854</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132892102</v>
+        <v>132889685</v>
       </c>
       <c r="B32" t="n">
         <v>58596</v>
@@ -4282,14 +4287,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R32" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4364,13 +4364,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892102</t>
+          <t>https://artportalen.se/Sighting/132889685</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132892513</v>
+        <v>132892102</v>
       </c>
       <c r="B33" t="n">
         <v>58596</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R33" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4485,38 +4485,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892513</t>
+          <t>https://artportalen.se/Sighting/132892102</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132850969</v>
+        <v>132892513</v>
       </c>
       <c r="B34" t="n">
-        <v>58624</v>
+        <v>58596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4524,24 +4524,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>652496</v>
+        <v>652363</v>
       </c>
       <c r="R34" t="n">
-        <v>6650123</v>
+        <v>6650308</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4565,22 +4575,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4595,24 +4595,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132850969</t>
+          <t>https://artportalen.se/Sighting/132892513</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132892118</v>
+        <v>132850969</v>
       </c>
       <c r="B35" t="n">
         <v>58624</v>
@@ -4645,34 +4645,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>652502</v>
+        <v>652496</v>
       </c>
       <c r="R35" t="n">
-        <v>6650117</v>
+        <v>6650123</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4696,12 +4686,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4716,44 +4716,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892118</t>
+          <t>https://artportalen.se/Sighting/132850969</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132666098</v>
+        <v>132892118</v>
       </c>
       <c r="B36" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4766,24 +4766,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>652496</v>
+        <v>652502</v>
       </c>
       <c r="R36" t="n">
-        <v>6650123</v>
+        <v>6650117</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4807,22 +4817,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4837,24 +4837,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132666098</t>
+          <t>https://artportalen.se/Sighting/132892118</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132850906</v>
+        <v>132666098</v>
       </c>
       <c r="B37" t="n">
         <v>58658</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>652397</v>
+        <v>652496</v>
       </c>
       <c r="R37" t="n">
-        <v>6650215</v>
+        <v>6650123</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4928,22 +4928,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4969,13 +4969,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132850906</t>
+          <t>https://artportalen.se/Sighting/132666098</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132889683</v>
+        <v>132850906</v>
       </c>
       <c r="B38" t="n">
         <v>58658</v>
@@ -5010,27 +5010,22 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>652469</v>
+        <v>652397</v>
       </c>
       <c r="R38" t="n">
-        <v>6650249</v>
+        <v>6650215</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5054,12 +5049,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5074,24 +5079,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132889683</t>
+          <t>https://artportalen.se/Sighting/132850906</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132892117</v>
+        <v>132889683</v>
       </c>
       <c r="B39" t="n">
         <v>58658</v>
@@ -5124,14 +5129,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>652502</v>
+        <v>652469</v>
       </c>
       <c r="R39" t="n">
-        <v>6650117</v>
+        <v>6650249</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5206,13 +5206,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892117</t>
+          <t>https://artportalen.se/Sighting/132889683</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132892522</v>
+        <v>132892117</v>
       </c>
       <c r="B40" t="n">
         <v>58658</v>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R40" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5327,13 +5327,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892522</t>
+          <t>https://artportalen.se/Sighting/132892117</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132892816</v>
+        <v>132892522</v>
       </c>
       <c r="B41" t="n">
         <v>58658</v>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>652547</v>
+        <v>652363</v>
       </c>
       <c r="R41" t="n">
-        <v>6650113</v>
+        <v>6650308</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5448,13 +5448,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892816</t>
+          <t>https://artportalen.se/Sighting/132892522</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132893090</v>
+        <v>132892816</v>
       </c>
       <c r="B42" t="n">
         <v>58658</v>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>652486</v>
+        <v>652547</v>
       </c>
       <c r="R42" t="n">
-        <v>6650197</v>
+        <v>6650113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5569,38 +5569,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893090</t>
+          <t>https://artportalen.se/Sighting/132892816</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132892115</v>
+        <v>132893090</v>
       </c>
       <c r="B43" t="n">
-        <v>58698</v>
+        <v>58658</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>652502</v>
+        <v>652486</v>
       </c>
       <c r="R43" t="n">
-        <v>6650117</v>
+        <v>6650197</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5690,13 +5690,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892115</t>
+          <t>https://artportalen.se/Sighting/132893090</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132892510</v>
+        <v>132892115</v>
       </c>
       <c r="B44" t="n">
         <v>58698</v>
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652363</v>
+        <v>652502</v>
       </c>
       <c r="R44" t="n">
-        <v>6650308</v>
+        <v>6650117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5811,13 +5811,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892510</t>
+          <t>https://artportalen.se/Sighting/132892115</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132893083</v>
+        <v>132892510</v>
       </c>
       <c r="B45" t="n">
         <v>58698</v>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R45" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5932,13 +5932,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893083</t>
+          <t>https://artportalen.se/Sighting/132892510</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133159810</v>
+        <v>132893083</v>
       </c>
       <c r="B46" t="n">
         <v>58698</v>
@@ -5968,32 +5968,37 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>652397</v>
+        <v>652486</v>
       </c>
       <c r="R46" t="n">
-        <v>6650215</v>
+        <v>6650197</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6017,22 +6022,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6047,44 +6042,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133159810</t>
+          <t>https://artportalen.se/Sighting/132893083</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132892807</v>
+        <v>133159810</v>
       </c>
       <c r="B47" t="n">
-        <v>58107</v>
+        <v>58698</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6094,32 +6089,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Roparhällarna, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>652547</v>
+        <v>652397</v>
       </c>
       <c r="R47" t="n">
-        <v>6650113</v>
+        <v>6650215</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6143,12 +6138,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6163,24 +6168,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Vilhelm Amcoff</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892807</t>
+          <t>https://artportalen.se/Sighting/133159810</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132893075</v>
+        <v>132892807</v>
       </c>
       <c r="B48" t="n">
         <v>58107</v>
@@ -6229,10 +6234,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>652486</v>
+        <v>652547</v>
       </c>
       <c r="R48" t="n">
-        <v>6650197</v>
+        <v>6650113</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6290,16 +6295,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132893075</t>
+          <t>https://artportalen.se/Sighting/132892807</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134462233</v>
+        <v>132893075</v>
       </c>
       <c r="B49" t="n">
-        <v>56854</v>
+        <v>58107</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6307,21 +6312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205995</v>
+        <v>205976</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6329,25 +6334,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storvreta NO, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>652363</v>
+        <v>652486</v>
       </c>
       <c r="R49" t="n">
-        <v>6650308</v>
+        <v>6650197</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6374,27 +6380,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Förbiflygande några gånger</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6420,46 +6411,46 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134462233</t>
+          <t>https://artportalen.se/Sighting/132893075</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132659867</v>
+        <v>134462233</v>
       </c>
       <c r="B50" t="n">
-        <v>56833</v>
+        <v>56854</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
@@ -6470,17 +6461,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Wängelistorpet, Upl</t>
+          <t>Storvreta NO, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>652369</v>
+        <v>652363</v>
       </c>
       <c r="R50" t="n">
-        <v>6650236</v>
+        <v>6650308</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6504,12 +6495,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Förbiflygande några gånger</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6535,13 +6541,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132659867</t>
+          <t>https://artportalen.se/Sighting/134462233</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134462221</v>
+        <v>132659867</v>
       </c>
       <c r="B51" t="n">
         <v>56833</v>
@@ -6565,8 +6571,16 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
@@ -6577,17 +6591,17 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storvreta NO, Upl</t>
+          <t>Wängelistorpet, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>652363</v>
+        <v>652369</v>
       </c>
       <c r="R51" t="n">
-        <v>6650308</v>
+        <v>6650236</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6611,27 +6625,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2019-07-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Förbiflygande många gånger</t>
+          <t>2019-07-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6657,16 +6656,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134462221</t>
+          <t>https://artportalen.se/Sighting/132659867</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>57751934</v>
+        <v>134462221</v>
       </c>
       <c r="B52" t="n">
-        <v>92328</v>
+        <v>56833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6674,48 +6673,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040162</v>
+        <v>205998</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Adolfsbergsskogen, Upl</t>
+          <t>Storvreta NO, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>652461</v>
+        <v>652363</v>
       </c>
       <c r="R52" t="n">
-        <v>6650195</v>
+        <v>6650308</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6739,17 +6732,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På tallstubbe</t>
+          <t>Förbiflygande många gånger</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6758,29 +6761,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6795,6 +6777,145 @@
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134462221</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>57751934</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>652461</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6650195</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/57751934</t>
         </is>
@@ -6853,6 +6974,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87510</v>
+        <v>87512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87510</v>
+        <v>87512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87512</v>
+        <v>87514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87512</v>
+        <v>87514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87514</v>
+        <v>87516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87514</v>
+        <v>87516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åke Berg, Håkan Lernefalk</t>
+          <t>Håkan Lernefalk, Åke Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87516</v>
+        <v>87517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87516</v>
+        <v>87517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk, Åke Berg</t>
+          <t>Åke Berg, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87517</v>
+        <v>87523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87517</v>
+        <v>87523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87523</v>
+        <v>87527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87523</v>
+        <v>87527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87527</v>
+        <v>87529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87527</v>
+        <v>87529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87529</v>
+        <v>87542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87529</v>
+        <v>87542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87542</v>
+        <v>87544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87542</v>
+        <v>87544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87544</v>
+        <v>87547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87544</v>
+        <v>87547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87547</v>
+        <v>87557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87547</v>
+        <v>87557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136753526</v>
       </c>
       <c r="B2" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136753515</v>
       </c>
       <c r="B4" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136753372</v>
       </c>
       <c r="B5" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136753380</v>
       </c>
       <c r="B6" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136772120</v>
       </c>
       <c r="B3" t="n">
-        <v>87558</v>
+        <v>87561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
